--- a/circuits/PumpControl_100x100/XGerber/ESP_PumpControl_BOM.xlsx
+++ b/circuits/PumpControl_100x100/XGerber/ESP_PumpControl_BOM.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
     <t>Comment</t>
   </si>
@@ -40,7 +40,7 @@
     <t>Analog Sensor</t>
   </si>
   <si>
-    <t>J2,J1,J3,J4</t>
+    <t>J3,J2,J4,J5</t>
   </si>
   <si>
     <t>Stiftleiste_1x04_G_2,54</t>
@@ -49,48 +49,39 @@
     <t>I2C 2</t>
   </si>
   <si>
+    <t>J7</t>
+  </si>
+  <si>
+    <t>Stiftleiste_1x04_G_2,54</t>
+  </si>
+  <si>
+    <t>I2C 3</t>
+  </si>
+  <si>
+    <t>J8</t>
+  </si>
+  <si>
+    <t>Stiftleiste_1x04_G_2,54</t>
+  </si>
+  <si>
+    <t>Header ADS1115</t>
+  </si>
+  <si>
+    <t>J9</t>
+  </si>
+  <si>
+    <t>1X10_BUCHSE</t>
+  </si>
+  <si>
+    <t>Header PCF8574</t>
+  </si>
+  <si>
     <t>J6</t>
   </si>
   <si>
-    <t>Stiftleiste_1x04_G_2,54</t>
-  </si>
-  <si>
-    <t>I2C 3</t>
-  </si>
-  <si>
-    <t>J7</t>
-  </si>
-  <si>
-    <t>Stiftleiste_1x04_G_2,54</t>
-  </si>
-  <si>
-    <t>Header ADS1115</t>
-  </si>
-  <si>
-    <t>J8</t>
-  </si>
-  <si>
-    <t>1X10_BUCHSE</t>
-  </si>
-  <si>
-    <t>Header PCF8574</t>
-  </si>
-  <si>
-    <t>J5</t>
-  </si>
-  <si>
     <t>1X06-90</t>
   </si>
   <si>
-    <t>Header GPIO</t>
-  </si>
-  <si>
-    <t>J9</t>
-  </si>
-  <si>
-    <t>2X08_BUCHSE</t>
-  </si>
-  <si>
     <t>NodeMCU ESP32 ( AZDelivery )</t>
   </si>
   <si>
@@ -107,6 +98,51 @@
   </si>
   <si>
     <t>TB6612 Shild</t>
+  </si>
+  <si>
+    <t>100nF</t>
+  </si>
+  <si>
+    <t>C1</t>
+  </si>
+  <si>
+    <t>0805</t>
+  </si>
+  <si>
+    <t>1mF</t>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
+    <t>D10R5,08_ELKO</t>
+  </si>
+  <si>
+    <t>ESP32 C3 Super Mini</t>
+  </si>
+  <si>
+    <t>X2</t>
+  </si>
+  <si>
+    <t>ESP32 C3 SUPER MINI ohne Sockelleiste</t>
+  </si>
+  <si>
+    <t>VCC Select</t>
+  </si>
+  <si>
+    <t>J1</t>
+  </si>
+  <si>
+    <t>Stiftleiste_1x03_G_2,54</t>
+  </si>
+  <si>
+    <t>K2X10_BUCHSE</t>
+  </si>
+  <si>
+    <t>K3</t>
+  </si>
+  <si>
+    <t>2X10_BUCHSE</t>
   </si>
 </sst>
 </file>
@@ -288,6 +324,50 @@
         <v>30</v>
       </c>
     </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" t="s">
+        <v>42</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
